--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.92183652380763</v>
+        <v>7.949798435118741</v>
       </c>
       <c r="D2" t="n">
-        <v>49.27301926304671</v>
+        <v>8.006865630245089</v>
       </c>
       <c r="E2" t="n">
-        <v>4.932134284143779</v>
+        <v>0.8014718211733639</v>
       </c>
       <c r="F2" t="n">
-        <v>7.382786714640609</v>
+        <v>1.1997028411291</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.75391125213041</v>
+        <v>6.785010578471192</v>
       </c>
       <c r="D3" t="n">
-        <v>41.61663436342155</v>
+        <v>6.762703084056001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.932134284143779</v>
+        <v>0.8014718211733639</v>
       </c>
       <c r="F3" t="n">
-        <v>7.382786714640609</v>
+        <v>1.1997028411291</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.76001163087358</v>
+        <v>8.736001890016956</v>
       </c>
       <c r="D4" t="n">
-        <v>59.63319374653643</v>
+        <v>9.690393983812172</v>
       </c>
       <c r="E4" t="n">
-        <v>4.932134284143779</v>
+        <v>0.8014718211733639</v>
       </c>
       <c r="F4" t="n">
-        <v>7.382786714640609</v>
+        <v>1.1997028411291</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
